--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/MathFunctions.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/MathFunctions.xlsx
@@ -551,12 +551,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I45"/>
+  <dimension ref="B2:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24.1" customWidth="1" min="3" max="3"/>
+    <col width="27.2" customWidth="1" min="3" max="3"/>
     <col width="10.4" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -574,10 +574,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="43.5" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>rint rounds to the nearest whole number and to the even one for halves. getExponent(x, y) with two arguments returns the length of the hypotenuse, the square root of x * x + y * y.</t>
+          <t>abs keeps the type of the number, so the absolute value of a BigDecimal or a BigInteger is exact. rint rounds to the nearest whole number and to the even one for halves. getExponent(x, y) with two arguments returns the length of the hypotenuse, the square root of x * x + y * y.</t>
         </is>
       </c>
     </row>
@@ -616,303 +616,297 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Signum</t>
+          <t>AbsDecimal</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>= signum(-3.2)</t>
+          <t>= abs((BigDecimal) -2.5)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Ceil</t>
+          <t>AbsBigInteger</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>= ceil(2.1)</t>
+          <t>= abs((BigInteger) -7)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Signum</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>= floor(-2.1)</t>
+          <t>= signum(-3.2)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Rint</t>
+          <t>Ceil</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>= rint(2.5)</t>
+          <t>= ceil(2.1)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Sqrt</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>= sqrt(16)</t>
+          <t>= floor(-2.1)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Cbrt</t>
+          <t>Rint</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>= cbrt(27)</t>
+          <t>= rint(2.5)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Pow</t>
+          <t>Sqrt</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>= pow(2, 10)</t>
+          <t>= sqrt(16)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>PowFraction</t>
+          <t>Cbrt</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>= pow(9, 0.5)</t>
+          <t>= cbrt(27)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>Pow</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>= exp(1)</t>
+          <t>= pow(2, 10)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Expm1</t>
+          <t>PowFraction</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>= expm1(0)</t>
+          <t>= pow(9, 0.5)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Log</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>= log(E)</t>
+          <t>= exp(1)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Log10</t>
+          <t>Expm1</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>= log10(1000)</t>
+          <t>= expm1(0)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Log1p</t>
+          <t>Log</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>= log1p(0)</t>
+          <t>= log(E)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Pi</t>
+          <t>Log10</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>= PI</t>
+          <t>= log10(1000)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Euler</t>
+          <t>Log1p</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>= E</t>
+          <t>= log1p(0)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>Pi</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>= PI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Euler</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>= E</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
           <t>Hypotenuse</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>= getExponent(3, 4)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Test BasicMath BasicMathTest</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$Abs</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>abs(-7.5)</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$Signum</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>signum(-3.2)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>-1</v>
-      </c>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Ceil</t>
+          <t>_res_.$Abs</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ceil(2.1)</t>
+          <t>abs(-7.5)</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Floor</t>
+          <t>_res_.$AbsDecimal</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>floor(-2.1)</t>
+          <t>abs((BigDecimal) -2.5)</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>-3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Rint</t>
+          <t>_res_.$AbsBigInteger</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>rint(2.5)</t>
+          <t>abs((BigInteger) -7)</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Sqrt</t>
+          <t>_res_.$Signum</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>sqrt(16)</t>
+          <t>signum(-3.2)</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Cbrt</t>
+          <t>_res_.$Ceil</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>cbrt(27)</t>
+          <t>ceil(2.1)</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
@@ -922,87 +916,87 @@
     <row r="36">
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Pow</t>
+          <t>_res_.$Floor</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>pow(2, 10)</t>
+          <t>floor(-2.1)</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>1024</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>_res_.$PowFraction</t>
+          <t>_res_.$Rint</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>pow(9, 0.5)</t>
+          <t>rint(2.5)</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Exp (6)</t>
+          <t>_res_.$Sqrt</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>exp(1)</t>
+          <t>sqrt(16)</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2.718282</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Expm1</t>
+          <t>_res_.$Cbrt</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>expm1(0)</t>
+          <t>cbrt(27)</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log</t>
+          <t>_res_.$Pow</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>log(E)</t>
+          <t>pow(2, 10)</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log10</t>
+          <t>_res_.$PowFraction</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>log10(1000)</t>
+          <t>pow(9, 0.5)</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
@@ -1012,67 +1006,127 @@
     <row r="42">
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log1p</t>
+          <t>_res_.$Exp (6)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>log1p(0)</t>
+          <t>exp(1)</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0</v>
+        <v>2.718282</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Pi (6)</t>
+          <t>_res_.$Expm1</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>expm1(0)</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>3.141593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Euler (6)</t>
+          <t>_res_.$Log</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>log(E)</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>2.718282</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="9" t="inlineStr">
         <is>
+          <t>_res_.$Log10</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>log10(1000)</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Log1p</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>log1p(0)</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Pi (6)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>3.141593</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Euler (6)</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>2.718282</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="9" t="inlineStr">
+        <is>
           <t>_res_.$Hypotenuse</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>getExponent(3, 4)</t>
         </is>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D49" s="10" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
@@ -2444,13 +2498,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I53"/>
+  <dimension ref="B2:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="30.4" customWidth="1" min="2" max="2"/>
-    <col width="27.2" customWidth="1" min="3" max="3"/>
-    <col width="13.6" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="33.5" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2470,7 +2524,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>abs(Integer.MIN_VALUE) stays negative, because 2147483648 does not fit into an Integer: convert to a Long first. getExponent(0) with a whole 0 uses the Float variant and returns -127.</t>
+          <t>abs(Integer.MIN_VALUE) stays negative, because 2147483648 does not fit into an Integer: convert to a Long first, and to a BigInteger for Long.MIN_VALUE. abs of a BigInteger or a BigDecimal is exact with any number of digits, which toString shows. getExponent(0) with a whole 0 uses the Float variant and returns -127.</t>
         </is>
       </c>
     </row>
@@ -2746,75 +2800,65 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>AbsOfLongLimit</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>= toString(abs((BigInteger) Long.MIN_VALUE))</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>AbsOfManyDigits</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>= toString(abs(new BigDecimal("-12345678901234567890.123456789")))</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Test MathEdgeCases MathEdgeCasesTest</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$AsinOutOfRange</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>isNaN(asin(2))</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$AcosOutOfRange</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>isNaN(acos(-2))</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>_res_.$LogOfZero</t>
+          <t>_res_.$AsinOutOfRange</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>log(0)</t>
+          <t>isNaN(asin(2))</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>-Infinity</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>_res_.$LogOfNegative</t>
+          <t>_res_.$AcosOutOfRange</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>isNaN(log(-1))</t>
+          <t>isNaN(acos(-2))</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -2826,271 +2870,339 @@
     <row r="37">
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log10OfFraction</t>
+          <t>_res_.$LogOfZero</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>log10(0.01)</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>-2</v>
+          <t>log(0)</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>-Infinity</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log1pOfMinusOne</t>
+          <t>_res_.$LogOfNegative</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>log1p(-1)</t>
+          <t>isNaN(log(-1))</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>-Infinity</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>_res_.$PowerOfZero</t>
+          <t>_res_.$Log10OfFraction</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>pow(0, -1)</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Infinity</t>
-        </is>
+          <t>log10(0.01)</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ExpUnderflow</t>
+          <t>_res_.$Log1pOfMinusOne</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>exp(-1000)</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0</v>
+          <t>log1p(-1)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>-Infinity</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Expm1Limit</t>
+          <t>_res_.$PowerOfZero</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>expm1(-180)</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>-1</v>
+          <t>pow(0, -1)</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Infinity</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TanhLimit</t>
+          <t>_res_.$ExpUnderflow</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>tanh(180)</t>
+          <t>exp(-1000)</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>_res_.$SinhOfBig</t>
+          <t>_res_.$Expm1Limit</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>sinh(180) &gt; 1e77</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>expm1(-180)</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>_res_.$CubeRootOfNegative</t>
+          <t>_res_.$TanhLimit</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>cbrt(-27)</t>
+          <t>tanh(180)</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>_res_.$SquareRootOfFraction</t>
+          <t>_res_.$SinhOfBig</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>sqrt(0.01)</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>0.1</v>
+          <t>sinh(180) &gt; 1e77</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ExponentOfZero</t>
+          <t>_res_.$CubeRootOfNegative</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>getExponent(0.0)</t>
+          <t>cbrt(-27)</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>-1023</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ExponentOfFraction</t>
+          <t>_res_.$SquareRootOfFraction</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>getExponent(0.01)</t>
+          <t>sqrt(0.01)</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>-7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ExponentOfNegative</t>
+          <t>_res_.$ExponentOfZero</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>getExponent(-180.0)</t>
+          <t>getExponent(0.0)</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>7</v>
+        <v>-1023</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>_res_.$HypotenuseNegative</t>
+          <t>_res_.$ExponentOfFraction</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>getExponent(-3.0, 4)</t>
+          <t>getExponent(0.01)</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>_res_.$HypotenuseOnAxis</t>
+          <t>_res_.$ExponentOfNegative</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>getExponent(180, 0)</t>
+          <t>getExponent(-180.0)</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>180</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>_res_.$AbsOfLong</t>
+          <t>_res_.$HypotenuseNegative</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>abs(-3L)</t>
+          <t>getExponent(-3.0, 4)</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>_res_.$AbsOfNegativeZero</t>
+          <t>_res_.$HypotenuseOnAxis</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>1 / abs(-0.0)</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>Infinity</t>
-        </is>
+          <t>getExponent(180, 0)</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="9" t="inlineStr">
         <is>
+          <t>_res_.$AbsOfLong</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>abs(-3L)</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$AbsOfNegativeZero</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>1 / abs(-0.0)</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Infinity</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="9" t="inlineStr">
+        <is>
           <t>_res_.$AbsOfIntegerLimit</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>abs(Integer.MIN_VALUE)</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n">
+      <c r="D55" s="10" t="n">
         <v>-2147483648</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$AbsOfLongLimit</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>toString(abs((BigInteger) Long.MIN_VALUE))</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>9223372036854775808</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$AbsOfManyDigits</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>toString(abs(new BigDecimal("-12345678901234567890.123456789")))</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>12345678901234567890.123456789</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/MathFunctions.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/MathFunctions.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I49"/>
+  <dimension ref="B2:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
     <row r="6" ht="43.5" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>abs keeps the type of the number, so the absolute value of a BigDecimal or a BigInteger is exact. rint rounds to the nearest whole number and to the even one for halves. getExponent(x, y) with two arguments returns the length of the hypotenuse, the square root of x * x + y * y.</t>
+          <t>abs keeps the type of the number, so the absolute value of a BigDecimal or a BigInteger is exact, and so is pow of a BigDecimal or a BigInteger and a whole exponent. rint rounds to the nearest whole number and to the even one for halves. getExponent(x, y) with two arguments returns the length of the hypotenuse, the square root of x * x + y * y.</t>
         </is>
       </c>
     </row>
@@ -736,267 +736,261 @@
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>PowDecimal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>= exp(1)</t>
+          <t>= pow((BigDecimal) 1.5, 2)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Expm1</t>
+          <t>PowBigInteger</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>= expm1(0)</t>
+          <t>= pow((BigInteger) -2, 3)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Log</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>= log(E)</t>
+          <t>= exp(1)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Log10</t>
+          <t>Expm1</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>= log10(1000)</t>
+          <t>= expm1(0)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Log1p</t>
+          <t>Log</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>= log1p(0)</t>
+          <t>= log(E)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Pi</t>
+          <t>Log10</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>= PI</t>
+          <t>= log10(1000)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Euler</t>
+          <t>Log1p</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>= E</t>
+          <t>= log1p(0)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
+          <t>Pi</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>= PI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Euler</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>= E</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>Hypotenuse</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>= getExponent(3, 4)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Test BasicMath BasicMathTest</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$Abs</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>abs(-7.5)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$AbsDecimal</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>abs((BigDecimal) -2.5)</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>_res_.$AbsBigInteger</t>
+          <t>_res_.$Abs</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>abs((BigInteger) -7)</t>
+          <t>abs(-7.5)</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Signum</t>
+          <t>_res_.$AbsDecimal</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>signum(-3.2)</t>
+          <t>abs((BigDecimal) -2.5)</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Ceil</t>
+          <t>_res_.$AbsBigInteger</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ceil(2.1)</t>
+          <t>abs((BigInteger) -7)</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Floor</t>
+          <t>_res_.$Signum</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>floor(-2.1)</t>
+          <t>signum(-3.2)</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Rint</t>
+          <t>_res_.$Ceil</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>rint(2.5)</t>
+          <t>ceil(2.1)</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Sqrt</t>
+          <t>_res_.$Floor</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>sqrt(16)</t>
+          <t>floor(-2.1)</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Cbrt</t>
+          <t>_res_.$Rint</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>cbrt(27)</t>
+          <t>rint(2.5)</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Pow</t>
+          <t>_res_.$Sqrt</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>pow(2, 10)</t>
+          <t>sqrt(16)</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1024</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>_res_.$PowFraction</t>
+          <t>_res_.$Cbrt</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>pow(9, 0.5)</t>
+          <t>cbrt(27)</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
@@ -1006,128 +1000,188 @@
     <row r="42">
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Exp (6)</t>
+          <t>_res_.$Pow</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>exp(1)</t>
+          <t>pow(2, 10)</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>2.718282</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Expm1</t>
+          <t>_res_.$PowFraction</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>expm1(0)</t>
+          <t>pow(9, 0.5)</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log</t>
+          <t>_res_.$PowDecimal</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>log(E)</t>
+          <t>pow((BigDecimal) 1.5, 2)</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log10</t>
+          <t>_res_.$PowBigInteger</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>log10(1000)</t>
+          <t>pow((BigInteger) -2, 3)</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Log1p</t>
+          <t>_res_.$Exp (6)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>log1p(0)</t>
+          <t>exp(1)</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0</v>
+        <v>2.718282</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Pi (6)</t>
+          <t>_res_.$Expm1</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>expm1(0)</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>3.141593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Euler (6)</t>
+          <t>_res_.$Log</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>log(E)</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>2.718282</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="9" t="inlineStr">
         <is>
+          <t>_res_.$Log10</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>log10(1000)</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Log1p</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>log1p(0)</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Pi (6)</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>3.141593</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Euler (6)</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>2.718282</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="9" t="inlineStr">
+        <is>
           <t>_res_.$Hypotenuse</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>getExponent(3, 4)</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D53" s="10" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3200,10 +3254,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B6:I6"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4048,8 +4102,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B6:I6"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:I6"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
